--- a/data/exports/王颖瑜伽/dist_order_2026-09-06.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-09-06.xlsx
@@ -5799,7 +5799,7 @@
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>百佳惠大瑞丰药房曹利红</t>
+          <t>丽红</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
